--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="C4" s="19" t="n">
-        <v>48017802.83319887</v>
+        <v>47969208.01585276</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>47878134.99482423</v>
+        <v>47766978.57629456</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>47738467.1564496</v>
+        <v>47564749.13673637</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>143634404.9844727</v>
+        <v>143300935.7288837</v>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
@@ -2125,16 +2125,16 @@
         </is>
       </c>
       <c r="C5" s="19" t="n">
-        <v>23662658.92030731</v>
+        <v>23638711.91481541</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>23593832.10553038</v>
+        <v>23539055.41306889</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>23525005.29075345</v>
+        <v>23439398.91132238</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>70781496.31659114</v>
+        <v>70617166.23920669</v>
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
@@ -2157,16 +2157,16 @@
         </is>
       </c>
       <c r="C6" s="19" t="n">
-        <v>2555009.402522537</v>
+        <v>2552423.690392716</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>2547577.728867731</v>
+        <v>2541663.137242608</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2540146.055212924</v>
+        <v>2530902.5840925</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>7642733.186603192</v>
+        <v>7624989.411727823</v>
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="C8" s="19" t="n">
-        <v>13861</v>
+        <v>13813</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>13821</v>
+        <v>13719</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>13781</v>
+        <v>13626</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>41463</v>
+        <v>41158</v>
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>第10期3年計41,463件。給付の見込件数による</t>
+          <t>第10期3年計41,158件。給付の見込件数による</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>**※ 標準給付費見込額（68行）は、上の加算4項目を入れると総給付費と合わせて第10期3年計3,101,160,492円になる（当方の算定による）。**受領したワークシートは加算4項目がすべて0で、標準給付費＝総給付費3,101,295,000円となっている。</t>
+          <t>**※ 標準給付費見込額（68行）は、上の加算4項目を入れると総給付費と合わせて第10期3年計3,093,948,167円になる（当方の算定による）。**受領したワークシートは加算4項目がすべて0で、標準給付費＝総給付費3,101,295,000円となっている。</t>
         </is>
       </c>
     </row>
@@ -3053,10 +3053,10 @@
         <v>3101295000</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>3101160491.817961</v>
+        <v>3093948167.011783</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>-134508.182038784</v>
+        <v>-7346832.988217354</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         <v>3101295000</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>2876614071.574327</v>
+        <v>2869935571.717914</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>-224680928.4256725</v>
+        <v>-231359428.2820859</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>包括的支援事業・任意事業費29,335,189円の事業別内訳（センター運営／任意事業／社会保障充実分6事業）</t>
+          <t>包括的支援事業・任意事業費29,335,189円の事業別内訳（センター運営／任意事業／社会保障充実分6事業）。**あわせて、保険者機能強化推進交付金及び介護保険保険者努力支援交付金を財源とする事業がこの額に含まれているかをご確認ください**</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>3_地域支援事業費 38・39・43〜48行（8欄）。5_保険料推計 88・89行の分割にも要る</t>
+          <t>3_地域支援事業費 38・39・43〜48行（8欄）。5_保険料推計 88・89行の分割にも要る。**交付金を財源とする事業は第1号被保険者負担分の算定基礎に含めない。含まれていれば保険料が過大になる**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
@@ -621,22 +621,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値（4_施策反映 21・33行）</t>
+          <t>**介護保険事業状況報告の設定 ― 令和8年度のチェック**</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>令和8年度</t>
+          <t>**令和8年5月のみチェック（9月25日に画面で確認済み）**</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>**令和7年度に切り替える**</t>
+          <t>**チェックを外す。**令和7年度（月報12か月）が最新になる</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>**令和8年度の列は1か月分である。**2_サービス別給付費 の人数・回数・日数を数えると、令和8年度は非ゼロ36件のうち31件（86.1％）が整数であるのに対し、令和6年度は46件中5件（10.9％）、令和7年度は40件中8件（20.0％）にとどまる。令和6・7年度は12分の1単位の小数（年間延べ÷12）である。**国保連月報でみると、令和8年度4〜6月提供分の給付額は前年の同じ月の96.0％である。****本件の算定は令和8年度をこの水準（0.9598）で置いている。入力値もこれにそろえている**</t>
+          <t>**令和8年度は令和8年5月の1か月分である（設定画面で確定）。**2_サービス別給付費 の人数・回数・日数を数えると、令和8年度は非ゼロ36件のうち31件（86.1％）が整数であるのに対し、令和6年度は46件中5件（10.9％）、令和7年度は40件中8件（20.0％）にとどまる。令和6・7年度は12分の1単位の小数（年間延べ÷12）である。**国保連月報でみると、令和8年度4〜6月提供分の給付額は前年の同じ月の96.0％である。****本件の算定は令和8年度をこの水準（0.9598）で置いている。入力値もこれにそろえている**</t>
         </is>
       </c>
     </row>
@@ -646,17 +646,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>認定率の伸び（4_施策反映 13行）</t>
+          <t>認定率の伸び（推計方法の設定（2）2）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>令和6年度→令和7年度</t>
+          <t>**令和6年度→令和7年度（9月25日に画面で確認済み）**</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>**断層の確認が取れるまで保留する**</t>
+          <t>**このままでよい。**完結年度どうしの伸びである</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,9 +175,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2544,7 +2541,7 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>**※ 調整交付金見込交付割合（95行）は入力欄ではない。**所得段階別加入割合（115〜127行）を入れると所得段階別加入割合補正係数（99行）が計算され、すでに入っている後期高齢者加入割合補正係数（96行）と合わせて自動で出る。**当方が第9期の公表値から逆算した6.148％と突き合わせる。**</t>
+          <t>**※ 調整交付金見込交付割合（95行）は入力欄ではない。**所得段階別加入割合（115〜127行）を入れると所得段階別加入割合補正係数（99行）が計算され、すでに入っている後期高齢者加入割合補正係数（96行）と合わせて自動で出る。**当方の算式による値（年度別6.107％・5.548％・4.945％）と突き合わせる。**</t>
         </is>
       </c>
     </row>
@@ -2618,9 +2615,9 @@
         <v>0.1524832994481557</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="F2" s="23" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="F2" s="22" t="n">
         <v>0.455</v>
       </c>
     </row>
@@ -2640,9 +2637,9 @@
         <v>0.08626198083067092</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="F3" s="23" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="F3" s="22" t="n">
         <v>0.6850000000000001</v>
       </c>
     </row>
@@ -2662,9 +2659,9 @@
         <v>0.07900087133313971</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="F4" s="23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F4" s="22" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
@@ -2683,10 +2680,10 @@
       <c r="D5" s="21" t="n">
         <v>0.126052860877142</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="22" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="22" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2705,10 +2702,10 @@
       <c r="D6" s="21" t="n">
         <v>0.1771710717397618</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2727,10 +2724,10 @@
       <c r="D7" s="21" t="n">
         <v>0.1426081905315132</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <v>1.2</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="22" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -2749,10 +2746,10 @@
       <c r="D8" s="21" t="n">
         <v>0.121405750798722</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="22" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -2771,10 +2768,10 @@
       <c r="D9" s="21" t="n">
         <v>0.0670926517571885</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="22" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2793,10 +2790,10 @@
       <c r="D10" s="21" t="n">
         <v>0.02236421725239617</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>1.7</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -2815,10 +2812,10 @@
       <c r="D11" s="21" t="n">
         <v>0.01045599767644496</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="22" t="n">
         <v>1.9</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="22" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -2837,10 +2834,10 @@
       <c r="D12" s="21" t="n">
         <v>0.004066221318617485</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <v>2.1</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="22" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -2859,10 +2856,10 @@
       <c r="D13" s="21" t="n">
         <v>0.002033110659308742</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="22" t="n">
         <v>2.3</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="22" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -2881,10 +2878,10 @@
       <c r="D14" s="21" t="n">
         <v>0.009003775776938717</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>2.4</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -2901,8 +2898,8 @@
       <c r="D15" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -2921,14 +2918,14 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>**※ 小野町の第1〜3段階の乗率（0.285／0.486／0.685）は国の標準（0.455／0.685／0.690）を下回る。**第4段階以上は国の標準と同じ。**乗率はこのシートには入れない。**見える化が求めるのは加入割合だけで、乗率は保険料額の算定に用いる。</t>
+          <t>**※ 小野町が実際に賦課する第1〜3段階の乗率（0.285／0.485／0.685）は国の標準（0.455／0.685／0.690）を下回る。**差は公費による低所得者軽減強化によるもので、**保険料基準額の算定では軽減前の標準割合を用いる。**第4段階以上は賦課する乗率と標準割合が一致する。**乗率はこのシートには入れない。**見える化が求めるのは加入割合だけで、乗率は保険料額の算定に用いる。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>**※ 第2段階の乗率を0.485としている資料があれば誤りである。**第9期の年額38,500円は0.486×79,200円＝38,491円の100円未満切上げであり、0.485では38,412円で38,400円になる。</t>
+          <t>**※ 第2段階の乗率は0.485である。**第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報 様式1 所得段階別の令和7年度は486となっているが、令和6年度は485であり、令和7年度の入力誤りとみる。</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2989,7 @@
       <c r="C2" s="19" t="n">
         <v>10284</v>
       </c>
-      <c r="D2" s="25" t="n">
+      <c r="D2" s="24" t="n">
         <v>9</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -3013,7 +3010,7 @@
       <c r="C3" s="19" t="n">
         <v>782</v>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="24" t="n">
         <v>-67</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -3034,7 +3031,7 @@
       <c r="C4" s="19" t="n">
         <v>772</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="24" t="n">
         <v>-69</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -3055,7 +3052,7 @@
       <c r="C5" s="19" t="n">
         <v>3093948167.011783</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>-7346832.988217354</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -3076,7 +3073,7 @@
       <c r="C6" s="19" t="n">
         <v>2869935571.717914</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>-231359428.2820859</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -3097,7 +3094,7 @@
       <c r="C7" s="19" t="n">
         <v>6600</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>-8.899848932060195</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3331,7 +3328,7 @@
           <t>見える化の第9期保険料基準額6,608.9円がどの段階の値か</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3351,7 +3348,7 @@
           <t>訪問型サービスA・通所型サービスA・配食・見守りの実施の有無</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>C</t>
         </is>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260925.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>**年報 様式4 の保有額は令和5・6年度末とも12,000千円。一方で令和4年度末は120,000千円、繰入金は全年度0円で系列に矛盾がある。基金運用状況調書で確認する**</t>
+          <t>**令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。年報 様式4 の保有額は財務書類と合わないため用いない。令和7年度末の残高は財産に関する調書で確認する**</t>
         </is>
       </c>
     </row>
